--- a/artfynd/A 33547-2019 artfynd.xlsx
+++ b/artfynd/A 33547-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33547-2019 artfynd.xlsx
+++ b/artfynd/A 33547-2019 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>125862674</v>
       </c>
       <c r="B5" t="n">
-        <v>58275</v>
+        <v>58276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33547-2019 artfynd.xlsx
+++ b/artfynd/A 33547-2019 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>125862672</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>125862674</v>
       </c>
       <c r="B5" t="n">
-        <v>58276</v>
+        <v>58277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33547-2019 artfynd.xlsx
+++ b/artfynd/A 33547-2019 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>125862672</v>
       </c>
       <c r="B4" t="n">
-        <v>57511</v>
+        <v>57515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>125862674</v>
       </c>
       <c r="B5" t="n">
-        <v>58277</v>
+        <v>58281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33547-2019 artfynd.xlsx
+++ b/artfynd/A 33547-2019 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>125862672</v>
       </c>
       <c r="B4" t="n">
-        <v>57515</v>
+        <v>57516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>125862674</v>
       </c>
       <c r="B5" t="n">
-        <v>58281</v>
+        <v>58284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
